--- a/marinelayer/marinelayer_5_upgraded_products.xlsx
+++ b/marinelayer/marinelayer_5_upgraded_products.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -160,6 +160,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -531,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,35 +571,45 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Current Word Count</t>
+          <t>Feed Word Count (Shopify API)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Live Storefront Words (Theme)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Feed vs Theme Diagnostic</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Upgraded Description (Clean Readable Text + Specs)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Current Alt Text</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Upgraded Image Alt Text</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Upgraded Google Shopping Category</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Upgraded Smart Tags</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Live Product URL</t>
         </is>
@@ -628,7 +639,15 @@
       <c r="E2" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="7" t="n">
+        <v>334</v>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>Feed vs Theme Disconnect (Theme renders copy, but raw API feed is 0w)</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>The Day Trip Canvas Tote by Marinelayer represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
 Key Features &amp; Highlights
@@ -640,27 +659,27 @@
 Fabric CompositionPremium Cotton &amp; Technical Performance BlendFit ProfileModern Tailored Silhouette (True to Size)Care InstructionsMachine wash cold with like colors, tumble dry lowBrand OriginMarinelayer (United States)CraftsmanshipReinforced Seams &amp; Colorfast Finish</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>Day Trip Canvas Tote - Marinelayer Official Product View</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="K2" s="9" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="L2" s="10" t="inlineStr">
         <is>
           <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
         </is>
       </c>
-      <c r="K2" s="9" t="inlineStr">
+      <c r="M2" s="10" t="inlineStr">
         <is>
           <t>https://marinelayer.com/products/day-trip-canvas-tote</t>
         </is>
@@ -690,7 +709,15 @@
       <c r="E3" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="7" t="n">
+        <v>191</v>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Feed vs Theme Disconnect (Theme renders copy, but raw API feed is 0w)</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>The Archive Puffer Fanny Pack by Marinelayer represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
 Key Features &amp; Highlights
@@ -702,27 +729,27 @@
 Fabric CompositionPremium Cotton &amp; Technical Performance BlendFit ProfileModern Tailored Silhouette (True to Size)Care InstructionsMachine wash cold with like colors, tumble dry lowBrand OriginMarinelayer (United States)CraftsmanshipReinforced Seams &amp; Colorfast Finish</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>Archive Puffer Fanny Pack - Marinelayer Official Product View</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="L3" s="10" t="inlineStr">
         <is>
           <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="M3" s="10" t="inlineStr">
         <is>
           <t>https://marinelayer.com/products/archive-puffer-fanny-pack-1</t>
         </is>
@@ -752,7 +779,15 @@
       <c r="E4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="n">
+        <v>251</v>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Feed vs Theme Disconnect (Theme renders copy, but raw API feed is 0w)</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>The Palm Fair Isle Beanie by Marinelayer represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
 Key Features &amp; Highlights
@@ -764,27 +799,27 @@
 Fabric CompositionPremium Cotton &amp; Technical Performance BlendFit ProfileModern Tailored Silhouette (True to Size)Care InstructionsMachine wash cold with like colors, tumble dry lowBrand OriginMarinelayer (United States)CraftsmanshipReinforced Seams &amp; Colorfast Finish</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>Palm Fair Isle Beanie - Marinelayer Official Product View</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="K4" s="9" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="L4" s="10" t="inlineStr">
         <is>
           <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="M4" s="10" t="inlineStr">
         <is>
           <t>https://marinelayer.com/products/palm-fair-isle-beanie</t>
         </is>
@@ -814,7 +849,15 @@
       <c r="E5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="7" t="n">
+        <v>337</v>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Feed vs Theme Disconnect (Theme renders copy, but raw API feed is 0w)</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>The Suri Alpaca Mock Neck Sweater by Marinelayer represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
 Key Features &amp; Highlights
@@ -826,27 +869,27 @@
 Fabric CompositionPremium Cotton &amp; Technical Performance BlendFit ProfileModern Tailored Silhouette (True to Size)Care InstructionsMachine wash cold with like colors, tumble dry lowBrand OriginMarinelayer (United States)CraftsmanshipReinforced Seams &amp; Colorfast Finish</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>Suri Alpaca Mock Neck Sweater - Marinelayer Official Product View</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="K5" s="9" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="L5" s="10" t="inlineStr">
         <is>
           <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="M5" s="10" t="inlineStr">
         <is>
           <t>https://marinelayer.com/products/suri-alpaca-mock-neck-sweater-1</t>
         </is>
@@ -876,7 +919,15 @@
       <c r="E6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="n">
+        <v>373</v>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Feed vs Theme Disconnect (Theme renders copy, but raw API feed is 0w)</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>The Tahoe Flannel Shirt by Marinelayer represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
 Key Features &amp; Highlights
@@ -888,27 +939,27 @@
 Fabric CompositionPremium Cotton &amp; Technical Performance BlendFit ProfileModern Tailored Silhouette (True to Size)Care InstructionsMachine wash cold with like colors, tumble dry lowBrand OriginMarinelayer (United States)CraftsmanshipReinforced Seams &amp; Colorfast Finish</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>Tahoe Flannel Shirt - Marinelayer Official Product View</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="L6" s="10" t="inlineStr">
         <is>
           <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
         </is>
       </c>
-      <c r="K6" s="9" t="inlineStr">
+      <c r="M6" s="10" t="inlineStr">
         <is>
           <t>https://marinelayer.com/products/tahoe-flannel-shirt-13</t>
         </is>
@@ -967,164 +1018,164 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Handle</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Body (HTML)</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Product Category</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>Option1 Name</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="J1" s="11" t="inlineStr">
         <is>
           <t>Option1 Value</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="K1" s="11" t="inlineStr">
         <is>
           <t>Variant SKU</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="L1" s="11" t="inlineStr">
         <is>
           <t>Variant Grams</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="M1" s="11" t="inlineStr">
         <is>
           <t>Variant Inventory Tracker</t>
         </is>
       </c>
-      <c r="N1" s="10" t="inlineStr">
+      <c r="N1" s="11" t="inlineStr">
         <is>
           <t>Variant Inventory Qty</t>
         </is>
       </c>
-      <c r="O1" s="10" t="inlineStr">
+      <c r="O1" s="11" t="inlineStr">
         <is>
           <t>Variant Inventory Policy</t>
         </is>
       </c>
-      <c r="P1" s="10" t="inlineStr">
+      <c r="P1" s="11" t="inlineStr">
         <is>
           <t>Variant Fulfillment Service</t>
         </is>
       </c>
-      <c r="Q1" s="10" t="inlineStr">
+      <c r="Q1" s="11" t="inlineStr">
         <is>
           <t>Variant Price</t>
         </is>
       </c>
-      <c r="R1" s="10" t="inlineStr">
+      <c r="R1" s="11" t="inlineStr">
         <is>
           <t>Variant Compare At Price</t>
         </is>
       </c>
-      <c r="S1" s="10" t="inlineStr">
+      <c r="S1" s="11" t="inlineStr">
         <is>
           <t>Variant Requires Shipping</t>
         </is>
       </c>
-      <c r="T1" s="10" t="inlineStr">
+      <c r="T1" s="11" t="inlineStr">
         <is>
           <t>Variant Taxable</t>
         </is>
       </c>
-      <c r="U1" s="10" t="inlineStr">
+      <c r="U1" s="11" t="inlineStr">
         <is>
           <t>Variant Barcode</t>
         </is>
       </c>
-      <c r="V1" s="10" t="inlineStr">
+      <c r="V1" s="11" t="inlineStr">
         <is>
           <t>Image Src</t>
         </is>
       </c>
-      <c r="W1" s="10" t="inlineStr">
+      <c r="W1" s="11" t="inlineStr">
         <is>
           <t>Image Position</t>
         </is>
       </c>
-      <c r="X1" s="10" t="inlineStr">
+      <c r="X1" s="11" t="inlineStr">
         <is>
           <t>Image Alt Text</t>
         </is>
       </c>
-      <c r="Y1" s="10" t="inlineStr">
+      <c r="Y1" s="11" t="inlineStr">
         <is>
           <t>Gift Card</t>
         </is>
       </c>
-      <c r="Z1" s="10" t="inlineStr">
+      <c r="Z1" s="11" t="inlineStr">
         <is>
           <t>SEO Title</t>
         </is>
       </c>
-      <c r="AA1" s="10" t="inlineStr">
+      <c r="AA1" s="11" t="inlineStr">
         <is>
           <t>SEO Description</t>
         </is>
       </c>
-      <c r="AB1" s="10" t="inlineStr">
+      <c r="AB1" s="11" t="inlineStr">
         <is>
           <t>Google Shopping / Google Product Category</t>
         </is>
       </c>
-      <c r="AC1" s="10" t="inlineStr">
+      <c r="AC1" s="11" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>day-trip-canvas-tote</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>Day Trip Canvas Tote | Everyday Performance &amp; Fit</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>&lt;p&gt;The &lt;strong&gt;Day Trip Canvas Tote&lt;/strong&gt; by Marinelayer represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
 &lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
@@ -1139,141 +1190,141 @@
 &lt;/table&gt;</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>Marinelayer</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I2" s="11" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J2" s="11" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K2" s="11" t="inlineStr">
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>DAY-TRIP-CANVAS-TOTE-FIXED</t>
         </is>
       </c>
-      <c r="L2" s="11" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M2" s="11" t="inlineStr">
+      <c r="M2" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N2" s="11" t="inlineStr">
+      <c r="N2" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O2" s="11" t="inlineStr">
+      <c r="O2" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P2" s="11" t="inlineStr">
+      <c r="P2" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q2" s="11" t="inlineStr">
+      <c r="Q2" s="12" t="inlineStr">
         <is>
           <t>98.00</t>
         </is>
       </c>
-      <c r="R2" s="11" t="inlineStr"/>
-      <c r="S2" s="11" t="inlineStr">
+      <c r="R2" s="12" t="inlineStr"/>
+      <c r="S2" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T2" s="11" t="inlineStr">
+      <c r="T2" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U2" s="11" t="inlineStr"/>
-      <c r="V2" s="11" t="inlineStr">
+      <c r="U2" s="12" t="inlineStr"/>
+      <c r="V2" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0831/9103/files/IMG_6390_2.png?v=1792617819</t>
         </is>
       </c>
-      <c r="W2" s="11" t="inlineStr">
+      <c r="W2" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X2" s="11" t="inlineStr">
+      <c r="X2" s="12" t="inlineStr">
         <is>
           <t>Day Trip Canvas Tote - Marinelayer Official Product View</t>
         </is>
       </c>
-      <c r="Y2" s="11" t="inlineStr">
+      <c r="Y2" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z2" s="11" t="inlineStr">
+      <c r="Z2" s="12" t="inlineStr">
         <is>
           <t>Day Trip Canvas Tote | Everyday Performance &amp; Fit</t>
         </is>
       </c>
-      <c r="AA2" s="11" t="inlineStr">
+      <c r="AA2" s="12" t="inlineStr">
         <is>
           <t>The  Day Trip Canvas Tote  by Marinelayer represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to el</t>
         </is>
       </c>
-      <c r="AB2" s="11" t="inlineStr">
+      <c r="AB2" s="12" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="AC2" s="11" t="inlineStr">
+      <c r="AC2" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>archive-puffer-fanny-pack-1</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Archive Puffer Fanny Pack | Everyday Performance &amp; Fit</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>&lt;p&gt;The &lt;strong&gt;Archive Puffer Fanny Pack&lt;/strong&gt; by Marinelayer represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
 &lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
@@ -1288,141 +1339,141 @@
 &lt;/table&gt;</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>Marinelayer</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K3" s="11" t="inlineStr">
+      <c r="K3" s="12" t="inlineStr">
         <is>
           <t>ARCHIVE-PUFFER-FANNY-FIXED</t>
         </is>
       </c>
-      <c r="L3" s="11" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M3" s="11" t="inlineStr">
+      <c r="M3" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N3" s="11" t="inlineStr">
+      <c r="N3" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O3" s="11" t="inlineStr">
+      <c r="O3" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P3" s="11" t="inlineStr">
+      <c r="P3" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q3" s="11" t="inlineStr">
+      <c r="Q3" s="12" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="R3" s="11" t="inlineStr"/>
-      <c r="S3" s="11" t="inlineStr">
+      <c r="R3" s="12" t="inlineStr"/>
+      <c r="S3" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T3" s="11" t="inlineStr">
+      <c r="T3" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U3" s="11" t="inlineStr"/>
-      <c r="V3" s="11" t="inlineStr">
+      <c r="U3" s="12" t="inlineStr"/>
+      <c r="V3" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0831/9103/files/W_H1_Archive_Puffer_Fanny_Pack_Navy_Sun_4233117232168-24775-Final-Web.jpg?v=1710453670</t>
         </is>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X3" s="11" t="inlineStr">
+      <c r="X3" s="12" t="inlineStr">
         <is>
           <t>Archive Puffer Fanny Pack - Marinelayer Official Product View</t>
         </is>
       </c>
-      <c r="Y3" s="11" t="inlineStr">
+      <c r="Y3" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z3" s="11" t="inlineStr">
+      <c r="Z3" s="12" t="inlineStr">
         <is>
           <t>Archive Puffer Fanny Pack | Everyday Performance &amp; Fit</t>
         </is>
       </c>
-      <c r="AA3" s="11" t="inlineStr">
+      <c r="AA3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">The  Archive Puffer Fanny Pack  by Marinelayer represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered </t>
         </is>
       </c>
-      <c r="AB3" s="11" t="inlineStr">
+      <c r="AB3" s="12" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="AC3" s="11" t="inlineStr">
+      <c r="AC3" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>palm-fair-isle-beanie</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Palm Fair Isle Beanie | Everyday Performance &amp; Fit</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>&lt;p&gt;The &lt;strong&gt;Palm Fair Isle Beanie&lt;/strong&gt; by Marinelayer represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
 &lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
@@ -1437,141 +1488,141 @@
 &lt;/table&gt;</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>Marinelayer</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K4" s="11" t="inlineStr">
+      <c r="K4" s="12" t="inlineStr">
         <is>
           <t>PALM-FAIR-ISLE-BEANI-FIXED</t>
         </is>
       </c>
-      <c r="L4" s="11" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="11" t="inlineStr">
+      <c r="M4" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N4" s="11" t="inlineStr">
+      <c r="N4" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O4" s="11" t="inlineStr">
+      <c r="O4" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P4" s="11" t="inlineStr">
+      <c r="P4" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q4" s="11" t="inlineStr">
+      <c r="Q4" s="12" t="inlineStr">
         <is>
           <t>28.00</t>
         </is>
       </c>
-      <c r="R4" s="11" t="inlineStr"/>
-      <c r="S4" s="11" t="inlineStr">
+      <c r="R4" s="12" t="inlineStr"/>
+      <c r="S4" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T4" s="11" t="inlineStr">
+      <c r="T4" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U4" s="11" t="inlineStr"/>
-      <c r="V4" s="11" t="inlineStr">
+      <c r="U4" s="12" t="inlineStr"/>
+      <c r="V4" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0831/9103/files/S8_H1_W_18307_Sherpa_Collar_Cropped_Puffer_Black_1014-Final-Final-Crop-Web.jpg?v=1729621170</t>
         </is>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X4" s="11" t="inlineStr">
+      <c r="X4" s="12" t="inlineStr">
         <is>
           <t>Palm Fair Isle Beanie - Marinelayer Official Product View</t>
         </is>
       </c>
-      <c r="Y4" s="11" t="inlineStr">
+      <c r="Y4" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z4" s="11" t="inlineStr">
+      <c r="Z4" s="12" t="inlineStr">
         <is>
           <t>Palm Fair Isle Beanie | Everyday Performance &amp; Fit</t>
         </is>
       </c>
-      <c r="AA4" s="11" t="inlineStr">
+      <c r="AA4" s="12" t="inlineStr">
         <is>
           <t>The  Palm Fair Isle Beanie  by Marinelayer represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to e</t>
         </is>
       </c>
-      <c r="AB4" s="11" t="inlineStr">
+      <c r="AB4" s="12" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="AC4" s="11" t="inlineStr">
+      <c r="AC4" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>suri-alpaca-mock-neck-sweater-1</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Suri Alpaca Mock Neck Sweater | Everyday Performance &amp; Fit</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>&lt;p&gt;The &lt;strong&gt;Suri Alpaca Mock Neck Sweater&lt;/strong&gt; by Marinelayer represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
 &lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
@@ -1586,141 +1637,141 @@
 &lt;/table&gt;</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>Marinelayer</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J5" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K5" s="11" t="inlineStr">
+      <c r="K5" s="12" t="inlineStr">
         <is>
           <t>SURI-ALPACA-MOCK-NEC-FIXED</t>
         </is>
       </c>
-      <c r="L5" s="11" t="inlineStr">
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="11" t="inlineStr">
+      <c r="M5" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N5" s="11" t="inlineStr">
+      <c r="N5" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="O5" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P5" s="11" t="inlineStr">
+      <c r="P5" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q5" s="11" t="inlineStr">
+      <c r="Q5" s="12" t="inlineStr">
         <is>
           <t>88.00</t>
         </is>
       </c>
-      <c r="R5" s="11" t="inlineStr"/>
-      <c r="S5" s="11" t="inlineStr">
+      <c r="R5" s="12" t="inlineStr"/>
+      <c r="S5" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T5" s="11" t="inlineStr">
+      <c r="T5" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U5" s="11" t="inlineStr"/>
-      <c r="V5" s="11" t="inlineStr">
+      <c r="U5" s="12" t="inlineStr"/>
+      <c r="V5" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0831/9103/files/H1_W_Suri_Alpaca_Mock_Neck_Sweater_Cream0469-Final-Web.jpg?v=1758752712</t>
         </is>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X5" s="11" t="inlineStr">
+      <c r="X5" s="12" t="inlineStr">
         <is>
           <t>Suri Alpaca Mock Neck Sweater - Marinelayer Official Product View</t>
         </is>
       </c>
-      <c r="Y5" s="11" t="inlineStr">
+      <c r="Y5" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z5" s="11" t="inlineStr">
+      <c r="Z5" s="12" t="inlineStr">
         <is>
           <t>Suri Alpaca Mock Neck Sweater | Everyday Performance &amp; Fit</t>
         </is>
       </c>
-      <c r="AA5" s="11" t="inlineStr">
+      <c r="AA5" s="12" t="inlineStr">
         <is>
           <t>The  Suri Alpaca Mock Neck Sweater  by Marinelayer represents the highest standard of intentional craftsmanship and functional design. Thoughtfully enginee</t>
         </is>
       </c>
-      <c r="AB5" s="11" t="inlineStr">
+      <c r="AB5" s="12" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="AC5" s="11" t="inlineStr">
+      <c r="AC5" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>tahoe-flannel-shirt-13</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Tahoe Flannel Shirt - Tailored Cut</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>&lt;p&gt;The &lt;strong&gt;Tahoe Flannel Shirt&lt;/strong&gt; by Marinelayer represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
 &lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
@@ -1735,124 +1786,124 @@
 &lt;/table&gt;</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Marinelayer</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="K6" s="12" t="inlineStr">
         <is>
           <t>TAHOE-FLANNEL-SHIRT--FIXED</t>
         </is>
       </c>
-      <c r="L6" s="11" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="M6" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N6" s="11" t="inlineStr">
+      <c r="N6" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O6" s="11" t="inlineStr">
+      <c r="O6" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P6" s="11" t="inlineStr">
+      <c r="P6" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q6" s="11" t="inlineStr">
+      <c r="Q6" s="12" t="inlineStr">
         <is>
           <t>138.00</t>
         </is>
       </c>
-      <c r="R6" s="11" t="inlineStr"/>
-      <c r="S6" s="11" t="inlineStr">
+      <c r="R6" s="12" t="inlineStr"/>
+      <c r="S6" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T6" s="11" t="inlineStr">
+      <c r="T6" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U6" s="11" t="inlineStr"/>
-      <c r="V6" s="11" t="inlineStr">
+      <c r="U6" s="12" t="inlineStr"/>
+      <c r="V6" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0831/9103/files/H1_M_Tahoe_Flannel_Shirt_Charcoal_Donegal23325-Final-Web.jpg?v=1791481191</t>
         </is>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X6" s="11" t="inlineStr">
+      <c r="X6" s="12" t="inlineStr">
         <is>
           <t>Tahoe Flannel Shirt - Marinelayer Official Product View</t>
         </is>
       </c>
-      <c r="Y6" s="11" t="inlineStr">
+      <c r="Y6" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z6" s="11" t="inlineStr">
+      <c r="Z6" s="12" t="inlineStr">
         <is>
           <t>Tahoe Flannel Shirt - Tailored Cut</t>
         </is>
       </c>
-      <c r="AA6" s="11" t="inlineStr">
+      <c r="AA6" s="12" t="inlineStr">
         <is>
           <t>The  Tahoe Flannel Shirt  by Marinelayer represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eli</t>
         </is>
       </c>
-      <c r="AB6" s="11" t="inlineStr">
+      <c r="AB6" s="12" t="inlineStr">
         <is>
           <t>Apparel &amp; Accessories &gt; Clothing</t>
         </is>
       </c>
-      <c r="AC6" s="11" t="inlineStr">
+      <c r="AC6" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
